--- a/nriss-patch-2/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -435,33 +435,54 @@
     <t>DiagnosticReport.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:composition</t>
+  </si>
+  <si>
+    <t>composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -469,6 +490,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -595,7 +619,17 @@
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260619134042</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -605,6 +639,21 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:typeResultat</t>
+  </si>
+  <si>
+    <t>typeResultat</t>
+  </si>
+  <si>
+    <t>Types de résultats</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260916095454</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -645,11 +694,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>The subject of the report - usually, but not always, the patient</t>
+    <t>Sujet concerné</t>
   </si>
   <si>
     <t>The subject of the report. Usually, but not always, this is a patient. However, diagnostic services also perform analyses on specimens collected from a variety of other sources.</t>
@@ -677,11 +726,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-encounter-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Health care event when test ordered</t>
+    <t>L’événement de soins auquel se rapporte ce compte rendu de laboratoire (moment où l’examen a été prescrit).</t>
   </si>
   <si>
     <t>The healthcare event  (e.g. a patient and healthcare provider interaction) which this DiagnosticReport is about.</t>
@@ -792,6 +841,10 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -802,6 +855,19 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer:organization</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Organization productrice du CR</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -845,20 +911,7 @@
     <t>DiagnosticReport.resultsInterpreter.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1044,9 +1097,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -1097,11 +1147,11 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-specimen-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Specimens this report is based on</t>
+    <t>Échantillons sur lesquels repose ce compte rendu.</t>
   </si>
   <si>
     <t>Details about the specimens on which this diagnostic report is based.</t>
@@ -1193,6 +1243,9 @@
     <t>DiagnosticReport.media.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
@@ -1276,9 +1329,6 @@
   </si>
   <si>
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Diagnosis codes provided as adjuncts to the report.</t>
@@ -1626,12 +1676,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN59"/>
+  <dimension ref="A1:AN62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.1484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2597,11 +2647,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2616,17 +2666,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2663,16 +2711,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>140</v>
@@ -2696,54 +2742,52 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
         <v>145</v>
       </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2791,7 +2835,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2800,7 +2844,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -2812,7 +2856,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -2840,25 +2884,25 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -2907,7 +2951,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2919,31 +2963,31 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2959,22 +3003,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3023,7 +3067,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3038,55 +3082,57 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
         <v>171</v>
       </c>
@@ -3098,7 +3144,7 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>80</v>
@@ -3113,13 +3159,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3137,13 +3183,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -3152,58 +3198,58 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3212,7 +3258,7 @@
         <v>80</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>80</v>
@@ -3227,11 +3273,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3249,13 +3297,13 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
@@ -3264,38 +3312,38 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3304,15 +3352,17 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3337,7 +3387,7 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="Y15" t="s" s="2">
         <v>193</v>
@@ -3349,25 +3399,23 @@
         <v>80</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3376,7 +3424,7 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>196</v>
@@ -3393,15 +3441,17 @@
         <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
@@ -3416,18 +3466,18 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3451,13 +3501,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3475,13 +3523,13 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -3490,32 +3538,32 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
@@ -3530,20 +3578,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3567,13 +3611,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3591,10 +3635,10 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>90</v>
@@ -3606,28 +3650,28 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3646,19 +3690,17 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3707,7 +3749,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3722,28 +3764,28 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3753,7 +3795,7 @@
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -3762,19 +3804,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3823,7 +3865,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3838,35 +3880,35 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>91</v>
@@ -3878,19 +3920,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3939,13 +3981,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -3954,38 +3996,38 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -3994,19 +4036,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4055,13 +4097,13 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -4070,56 +4112,60 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4155,59 +4201,59 @@
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -4219,19 +4265,23 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>136</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4267,19 +4317,19 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>267</v>
+        <v>80</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4291,52 +4341,50 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C24" t="s" s="2">
         <v>271</v>
       </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>273</v>
@@ -4344,8 +4392,12 @@
       <c r="M24" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4393,7 +4445,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4405,27 +4457,27 @@
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4448,13 +4500,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4505,7 +4557,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4526,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -4534,10 +4586,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4545,7 +4597,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4560,13 +4612,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4605,19 +4657,19 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4646,13 +4698,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>80</v>
@@ -4662,7 +4714,7 @@
         <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -4674,13 +4726,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4731,7 +4783,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4760,10 +4812,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4786,13 +4838,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4843,7 +4895,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4864,7 +4916,7 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -4872,10 +4924,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4883,10 +4935,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -4898,13 +4950,13 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4943,19 +4995,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4984,12 +5036,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5010,24 +5064,22 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>136</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>80</v>
@@ -5069,19 +5121,19 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5090,7 +5142,7 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5098,10 +5150,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5124,13 +5176,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5142,7 +5194,7 @@
         <v>80</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>80</v>
@@ -5157,11 +5209,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5179,7 +5233,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5191,7 +5245,7 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5200,7 +5254,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>133</v>
+        <v>282</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5208,14 +5262,12 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5224,7 +5276,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5236,13 +5288,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5281,19 +5333,19 @@
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5325,7 +5377,7 @@
         <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5333,7 +5385,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -5348,22 +5400,24 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>80</v>
@@ -5405,10 +5459,10 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5426,7 +5480,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>262</v>
+        <v>133</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5434,10 +5488,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5448,7 +5502,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5460,13 +5514,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5478,7 +5532,7 @@
         <v>80</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>80</v>
@@ -5493,43 +5547,41 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>267</v>
+        <v>80</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5538,7 +5590,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5546,18 +5598,20 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
@@ -5572,24 +5626,22 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>80</v>
@@ -5631,19 +5683,19 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5652,7 +5704,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5660,10 +5712,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5686,13 +5738,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5743,7 +5795,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5755,7 +5807,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -5764,7 +5816,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>133</v>
+        <v>282</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5772,23 +5824,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -5800,13 +5850,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="M37" t="s" s="2">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5845,19 +5895,19 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5886,10 +5936,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5897,7 +5947,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -5912,22 +5962,24 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>80</v>
@@ -5969,10 +6021,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>90</v>
@@ -5990,7 +6042,7 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>262</v>
+        <v>133</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -5998,10 +6050,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6012,7 +6064,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6024,13 +6076,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6069,31 +6121,31 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>267</v>
+        <v>80</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6102,7 +6154,7 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6110,12 +6162,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6136,24 +6190,22 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>288</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>307</v>
+        <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>80</v>
@@ -6195,19 +6247,19 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6216,7 +6268,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6224,10 +6276,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6250,13 +6302,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6307,7 +6359,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6319,7 +6371,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6328,7 +6380,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>133</v>
+        <v>282</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6336,10 +6388,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6347,10 +6399,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6362,24 +6414,22 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>288</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>80</v>
@@ -6409,31 +6459,31 @@
         <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -6442,7 +6492,7 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -6450,10 +6500,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6461,10 +6511,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -6476,22 +6526,24 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>318</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>80</v>
@@ -6533,10 +6585,10 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -6545,7 +6597,7 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -6562,10 +6614,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6585,20 +6637,18 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6647,7 +6697,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6656,7 +6706,7 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -6676,10 +6726,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6687,7 +6737,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>90</v>
@@ -6699,19 +6749,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6719,7 +6769,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>80</v>
@@ -6737,13 +6787,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -6761,10 +6811,10 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>90</v>
@@ -6773,7 +6823,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -6790,7 +6840,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>333</v>
@@ -6804,7 +6854,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -6813,20 +6863,18 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>149</v>
+        <v>334</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -6875,7 +6923,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6896,7 +6944,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>338</v>
+        <v>133</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -6904,10 +6952,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6930,16 +6978,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6989,7 +7037,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6998,7 +7046,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -7018,10 +7066,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7032,7 +7080,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7041,23 +7089,21 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>345</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7081,13 +7127,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7105,13 +7151,13 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
@@ -7123,57 +7169,55 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>353</v>
+        <v>156</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7221,13 +7265,13 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7239,10 +7283,10 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -7250,10 +7294,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7264,7 +7308,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7273,19 +7317,19 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7335,13 +7379,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -7356,7 +7400,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>365</v>
+        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -7364,14 +7408,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7387,20 +7431,22 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7449,7 +7495,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7467,35 +7513,35 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>359</v>
+        <v>222</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -7504,16 +7550,20 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>258</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>259</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7561,28 +7611,28 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>261</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>262</v>
+        <v>374</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7590,14 +7640,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7616,16 +7666,16 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>136</v>
+        <v>376</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>137</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7675,7 +7725,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>269</v>
+        <v>375</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7687,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -7696,22 +7746,22 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>262</v>
+        <v>380</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7721,28 +7771,26 @@
         <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>383</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>145</v>
+        <v>386</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -7791,7 +7839,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7803,16 +7851,16 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>374</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -7820,10 +7868,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7846,20 +7894,16 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -7907,7 +7951,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7919,7 +7963,7 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -7928,49 +7972,51 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>386</v>
+        <v>282</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>388</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8019,19 +8065,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>387</v>
+        <v>285</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8040,13 +8086,13 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>391</v>
+        <v>282</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>392</v>
       </c>
@@ -8062,19 +8108,19 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I57" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>394</v>
@@ -8082,9 +8128,11 @@
       <c r="M57" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N57" s="2"/>
+      <c r="N57" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8133,28 +8181,28 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>398</v>
+        <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -8162,10 +8210,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8176,7 +8224,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8188,16 +8236,20 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8221,13 +8273,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8245,13 +8297,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -8263,10 +8315,10 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8274,10 +8326,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8297,23 +8349,19 @@
         <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8361,13 +8409,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8379,17 +8427,359 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN59">
+  <autoFilter ref="A1:AN62">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8399,7 +8789,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
